--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/64.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/64.xlsx
@@ -426,13 +426,13 @@
         <v>-3.595964494448142</v>
       </c>
       <c r="E2">
-        <v>-6.512187708859982</v>
+        <v>-8.674968781027314</v>
       </c>
       <c r="F2">
-        <v>-3.609239996349899</v>
+        <v>-4.609531740130831</v>
       </c>
       <c r="G2">
-        <v>-5.648371186134352</v>
+        <v>-7.697684949127237</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.399479947974047</v>
       </c>
       <c r="E3">
-        <v>-5.269085365962408</v>
+        <v>-9.055111531601202</v>
       </c>
       <c r="F3">
-        <v>-3.645606982067603</v>
+        <v>-4.330089452103043</v>
       </c>
       <c r="G3">
-        <v>-5.589618934448906</v>
+        <v>-7.748952057348391</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.312464468616128</v>
       </c>
       <c r="E4">
-        <v>-6.264770002976904</v>
+        <v>-9.649269963777591</v>
       </c>
       <c r="F4">
-        <v>-3.404760816438452</v>
+        <v>-3.958168227226718</v>
       </c>
       <c r="G4">
-        <v>-5.478437573058022</v>
+        <v>-7.368643206887995</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.147970422638418</v>
       </c>
       <c r="E5">
-        <v>-8.533236601535247</v>
+        <v>-8.649935376712913</v>
       </c>
       <c r="F5">
-        <v>-4.006313769044828</v>
+        <v>-4.113286650340148</v>
       </c>
       <c r="G5">
-        <v>-4.930029151750054</v>
+        <v>-7.351335674808686</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.854108629481641</v>
       </c>
       <c r="E6">
-        <v>-9.503824435599235</v>
+        <v>-11.02226252663718</v>
       </c>
       <c r="F6">
-        <v>-3.504342175398592</v>
+        <v>-4.248460471496374</v>
       </c>
       <c r="G6">
-        <v>-4.769285613090741</v>
+        <v>-6.831295318226732</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.345258388858837</v>
       </c>
       <c r="E7">
-        <v>-8.408372987721753</v>
+        <v>-11.27584348564469</v>
       </c>
       <c r="F7">
-        <v>-3.891456486809663</v>
+        <v>-4.015514445787723</v>
       </c>
       <c r="G7">
-        <v>-4.830169856103478</v>
+        <v>-7.25151941625412</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.577434266081034</v>
       </c>
       <c r="E8">
-        <v>-9.558247636223419</v>
+        <v>-12.67215768964378</v>
       </c>
       <c r="F8">
-        <v>-3.534883253172407</v>
+        <v>-4.1049872373315</v>
       </c>
       <c r="G8">
-        <v>-4.276322208474487</v>
+        <v>-6.949577799799353</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.510781656333788</v>
       </c>
       <c r="E9">
-        <v>-9.59012356476341</v>
+        <v>-11.12690650400642</v>
       </c>
       <c r="F9">
-        <v>-3.60634650901192</v>
+        <v>-3.932898051236917</v>
       </c>
       <c r="G9">
-        <v>-4.271220657798469</v>
+        <v>-7.51565791319595</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.136755859320759</v>
       </c>
       <c r="E10">
-        <v>-10.18576280794031</v>
+        <v>-12.3876653670599</v>
       </c>
       <c r="F10">
-        <v>-3.55537789108507</v>
+        <v>-3.958873167886501</v>
       </c>
       <c r="G10">
-        <v>-4.639121583577676</v>
+        <v>-7.002606118247398</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.468379245937069</v>
       </c>
       <c r="E11">
-        <v>-11.76653987216784</v>
+        <v>-13.56160885491234</v>
       </c>
       <c r="F11">
-        <v>-3.345887916754089</v>
+        <v>-3.997947258276553</v>
       </c>
       <c r="G11">
-        <v>-4.270250667955463</v>
+        <v>-6.316207537771528</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.549439315864244</v>
       </c>
       <c r="E12">
-        <v>-11.95038685993124</v>
+        <v>-13.04601491829502</v>
       </c>
       <c r="F12">
-        <v>-3.349614741699284</v>
+        <v>-3.5583459314893</v>
       </c>
       <c r="G12">
-        <v>-4.07376316910864</v>
+        <v>-6.033112857071831</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.444761262982962</v>
       </c>
       <c r="E13">
-        <v>-12.66826320199718</v>
+        <v>-14.16103390235965</v>
       </c>
       <c r="F13">
-        <v>-3.053876810123624</v>
+        <v>-3.602861567348343</v>
       </c>
       <c r="G13">
-        <v>-3.45531684637185</v>
+        <v>-5.418566356980302</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.245435686852243</v>
       </c>
       <c r="E14">
-        <v>-13.07147399916614</v>
+        <v>-15.28116100510492</v>
       </c>
       <c r="F14">
-        <v>-2.858675345123532</v>
+        <v>-3.576135949831823</v>
       </c>
       <c r="G14">
-        <v>-3.488855983230206</v>
+        <v>-5.411759875351561</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.051206991271432</v>
       </c>
       <c r="E15">
-        <v>-14.2222905702614</v>
+        <v>-16.02383074236286</v>
       </c>
       <c r="F15">
-        <v>-2.733383118715301</v>
+        <v>-3.119781720690352</v>
       </c>
       <c r="G15">
-        <v>-2.968229660087802</v>
+        <v>-5.2044535136824</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.9546124941424341</v>
       </c>
       <c r="E16">
-        <v>-14.64206199687641</v>
+        <v>-16.24297265654205</v>
       </c>
       <c r="F16">
-        <v>-2.398238921421066</v>
+        <v>-3.253312889286827</v>
       </c>
       <c r="G16">
-        <v>-3.012938577595659</v>
+        <v>-4.913886931700567</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.03448306739478525</v>
       </c>
       <c r="E17">
-        <v>-15.852111007992</v>
+        <v>-17.89265045279628</v>
       </c>
       <c r="F17">
-        <v>-2.376570486898636</v>
+        <v>-2.712599380579061</v>
       </c>
       <c r="G17">
-        <v>-2.499297505541116</v>
+        <v>-4.435297915815828</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.6546734353753554</v>
       </c>
       <c r="E18">
-        <v>-17.08327629340536</v>
+        <v>-17.68292323607904</v>
       </c>
       <c r="F18">
-        <v>-1.799444432266012</v>
+        <v>-2.402623470084083</v>
       </c>
       <c r="G18">
-        <v>-2.4143389753668</v>
+        <v>-4.456429127992997</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.08550054725538</v>
       </c>
       <c r="E19">
-        <v>-17.46393529001612</v>
+        <v>-19.23086433527696</v>
       </c>
       <c r="F19">
-        <v>-1.403993431313167</v>
+        <v>-2.285910644866647</v>
       </c>
       <c r="G19">
-        <v>-1.397044747149696</v>
+        <v>-3.709527017241406</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.252141214660516</v>
       </c>
       <c r="E20">
-        <v>-18.42686547453314</v>
+        <v>-19.76640619989806</v>
       </c>
       <c r="F20">
-        <v>-1.299343292215297</v>
+        <v>-1.859934305120641</v>
       </c>
       <c r="G20">
-        <v>-1.645504500417538</v>
+        <v>-3.746234346180845</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.169881490885274</v>
       </c>
       <c r="E21">
-        <v>-19.12697208459298</v>
+        <v>-19.49829789627394</v>
       </c>
       <c r="F21">
-        <v>-1.196443493439543</v>
+        <v>-1.58381128527587</v>
       </c>
       <c r="G21">
-        <v>-1.027564691148257</v>
+        <v>-3.538636656504227</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8728771869902092</v>
       </c>
       <c r="E22">
-        <v>-20.10156761815376</v>
+        <v>-21.54539909991533</v>
       </c>
       <c r="F22">
-        <v>-0.6204150256156282</v>
+        <v>-1.414484704469623</v>
       </c>
       <c r="G22">
-        <v>-2.315515880474016</v>
+        <v>-3.224214283366407</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.4072439066437193</v>
       </c>
       <c r="E23">
-        <v>-21.22988673037891</v>
+        <v>-21.68711316551137</v>
       </c>
       <c r="F23">
-        <v>-0.5811189327616253</v>
+        <v>-1.274975208327144</v>
       </c>
       <c r="G23">
-        <v>-1.467311076220727</v>
+        <v>-3.386844832983104</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.1725888626707183</v>
       </c>
       <c r="E24">
-        <v>-20.25493797584554</v>
+        <v>-22.75894862143885</v>
       </c>
       <c r="F24">
-        <v>-0.5056198709356728</v>
+        <v>-0.9490747628807489</v>
       </c>
       <c r="G24">
-        <v>-1.726748598496792</v>
+        <v>-3.264003730202907</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.8072272434835441</v>
       </c>
       <c r="E25">
-        <v>-21.76827247667683</v>
+        <v>-22.6313996225388</v>
       </c>
       <c r="F25">
-        <v>-0.4198192320885056</v>
+        <v>-0.9228312551926577</v>
       </c>
       <c r="G25">
-        <v>-0.9780654142450741</v>
+        <v>-3.49469909610702</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.438630172499065</v>
       </c>
       <c r="E26">
-        <v>-21.54572967851789</v>
+        <v>-22.5732449593323</v>
       </c>
       <c r="F26">
-        <v>-0.4298565599082272</v>
+        <v>-1.308520774670913</v>
       </c>
       <c r="G26">
-        <v>-1.878355031467716</v>
+        <v>-3.680420700860134</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.013619064183056</v>
       </c>
       <c r="E27">
-        <v>-22.49831682840139</v>
+        <v>-23.62641404540016</v>
       </c>
       <c r="F27">
-        <v>-0.2665008513413591</v>
+        <v>-1.089249438047676</v>
       </c>
       <c r="G27">
-        <v>-2.369130165482513</v>
+        <v>-3.768451417294894</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.486499796240466</v>
       </c>
       <c r="E28">
-        <v>-22.3474235459918</v>
+        <v>-23.76148936810096</v>
       </c>
       <c r="F28">
-        <v>-0.389660860054784</v>
+        <v>-1.009653271047477</v>
       </c>
       <c r="G28">
-        <v>-2.193869884633496</v>
+        <v>-3.969169793340906</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.823635247638822</v>
       </c>
       <c r="E29">
-        <v>-21.77662751122099</v>
+        <v>-23.29933142477415</v>
       </c>
       <c r="F29">
-        <v>-0.4449154509237194</v>
+        <v>-1.16194696131736</v>
       </c>
       <c r="G29">
-        <v>-2.160542622689653</v>
+        <v>-4.136421864530425</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.003902592859455</v>
       </c>
       <c r="E30">
-        <v>-22.00926880641703</v>
+        <v>-24.08639832120329</v>
       </c>
       <c r="F30">
-        <v>-0.6254407306484129</v>
+        <v>-1.139908246565879</v>
       </c>
       <c r="G30">
-        <v>-2.603513479117374</v>
+        <v>-4.468853605401881</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.020941214521442</v>
       </c>
       <c r="E31">
-        <v>-22.22706123534193</v>
+        <v>-23.89953989822479</v>
       </c>
       <c r="F31">
-        <v>-0.3389390956139675</v>
+        <v>-1.381996134931827</v>
       </c>
       <c r="G31">
-        <v>-2.37077881716107</v>
+        <v>-4.328512958901097</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.881291082353095</v>
       </c>
       <c r="E32">
-        <v>-22.49534162097835</v>
+        <v>-23.01312281054137</v>
       </c>
       <c r="F32">
-        <v>-0.402097139873013</v>
+        <v>-1.414024132193667</v>
       </c>
       <c r="G32">
-        <v>-2.557685597217243</v>
+        <v>-4.034549757195973</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.600920268926529</v>
       </c>
       <c r="E33">
-        <v>-22.08827256395485</v>
+        <v>-22.21972510744951</v>
       </c>
       <c r="F33">
-        <v>-1.051527243258992</v>
+        <v>-1.32953148547552</v>
       </c>
       <c r="G33">
-        <v>-2.033877839811598</v>
+        <v>-3.774897049459855</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.204675346742572</v>
       </c>
       <c r="E34">
-        <v>-21.6804608371941</v>
+        <v>-23.2506548576657</v>
       </c>
       <c r="F34">
-        <v>-0.8949906551519692</v>
+        <v>-1.716271374820525</v>
       </c>
       <c r="G34">
-        <v>-2.328393902621781</v>
+        <v>-3.963896094296847</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-1.721886583298084</v>
       </c>
       <c r="E35">
-        <v>-21.22914858911566</v>
+        <v>-23.51544831831621</v>
       </c>
       <c r="F35">
-        <v>-0.6430783293888199</v>
+        <v>-1.548855009245134</v>
       </c>
       <c r="G35">
-        <v>-2.460378732181444</v>
+        <v>-3.260759395574421</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-1.186831052475654</v>
       </c>
       <c r="E36">
-        <v>-22.01149681562881</v>
+        <v>-22.66331630734486</v>
       </c>
       <c r="F36">
-        <v>-1.114276074021054</v>
+        <v>-1.813105039105579</v>
       </c>
       <c r="G36">
-        <v>-1.48451598138832</v>
+        <v>-3.59177091240953</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.6367920227462209</v>
       </c>
       <c r="E37">
-        <v>-20.87249503321956</v>
+        <v>-22.05680419807555</v>
       </c>
       <c r="F37">
-        <v>-0.9549694253190703</v>
+        <v>-2.084652157417285</v>
       </c>
       <c r="G37">
-        <v>-1.634622737229954</v>
+        <v>-2.970202745229207</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.1071287266505746</v>
       </c>
       <c r="E38">
-        <v>-19.70273132687621</v>
+        <v>-22.42395475672143</v>
       </c>
       <c r="F38">
-        <v>-1.140923825001712</v>
+        <v>-1.802649385747443</v>
       </c>
       <c r="G38">
-        <v>-0.8183547657940142</v>
+        <v>-2.746826995512423</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.3685986228021724</v>
       </c>
       <c r="E39">
-        <v>-20.09098910287184</v>
+        <v>-21.74762263520186</v>
       </c>
       <c r="F39">
-        <v>-1.18404449015444</v>
+        <v>-1.82590000200922</v>
       </c>
       <c r="G39">
-        <v>-0.9968957972724487</v>
+        <v>-2.173632519751931</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.7628402042643526</v>
       </c>
       <c r="E40">
-        <v>-19.28214024646581</v>
+        <v>-21.68198693293468</v>
       </c>
       <c r="F40">
-        <v>-1.308566334878067</v>
+        <v>-1.856509834277467</v>
       </c>
       <c r="G40">
-        <v>-0.8699264442047808</v>
+        <v>-2.432364895828132</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.059825442556554</v>
       </c>
       <c r="E41">
-        <v>-19.22240967430464</v>
+        <v>-20.56017523785855</v>
       </c>
       <c r="F41">
-        <v>-1.487242698559712</v>
+        <v>-2.125288548729017</v>
       </c>
       <c r="G41">
-        <v>-0.5705339478152518</v>
+        <v>-1.629451665097612</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.254771645539681</v>
       </c>
       <c r="E42">
-        <v>-18.98028122606252</v>
+        <v>-19.94308914178133</v>
       </c>
       <c r="F42">
-        <v>-1.571856286918668</v>
+        <v>-1.740122557449331</v>
       </c>
       <c r="G42">
-        <v>-0.2216322428859221</v>
+        <v>-1.886148055667161</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.352767767959023</v>
       </c>
       <c r="E43">
-        <v>-18.09747333216321</v>
+        <v>-21.20379819162072</v>
       </c>
       <c r="F43">
-        <v>-1.664025414358557</v>
+        <v>-1.958394882984793</v>
       </c>
       <c r="G43">
-        <v>-0.2407208484653597</v>
+        <v>-2.22832935315177</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>1.369049026419263</v>
       </c>
       <c r="E44">
-        <v>-17.85841066082429</v>
+        <v>-19.6714984416453</v>
       </c>
       <c r="F44">
-        <v>-1.670453545404282</v>
+        <v>-2.167325709318884</v>
       </c>
       <c r="G44">
-        <v>-0.7933435942448205</v>
+        <v>-1.497966727914378</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>1.324633046658619</v>
       </c>
       <c r="E45">
-        <v>-17.995800033743</v>
+        <v>-20.43014916367631</v>
       </c>
       <c r="F45">
-        <v>-1.691190894965964</v>
+        <v>-2.142785325010948</v>
       </c>
       <c r="G45">
-        <v>-0.283450059740733</v>
+        <v>-2.024019035195649</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>1.242556822893857</v>
       </c>
       <c r="E46">
-        <v>-16.95784662034091</v>
+        <v>-19.38164893431036</v>
       </c>
       <c r="F46">
-        <v>-1.74500164145182</v>
+        <v>-2.144175325512846</v>
       </c>
       <c r="G46">
-        <v>-0.824724255411572</v>
+        <v>-1.811286689387621</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>1.147384328705788</v>
       </c>
       <c r="E47">
-        <v>-16.99164262186015</v>
+        <v>-18.95160240017194</v>
       </c>
       <c r="F47">
-        <v>-1.960793006615897</v>
+        <v>-2.389604019614283</v>
       </c>
       <c r="G47">
-        <v>-0.8276011194851987</v>
+        <v>-1.989804547047281</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>1.061866659575939</v>
       </c>
       <c r="E48">
-        <v>-16.50362256347554</v>
+        <v>-18.23014403516593</v>
       </c>
       <c r="F48">
-        <v>-2.206736116874473</v>
+        <v>-2.341460962898382</v>
       </c>
       <c r="G48">
-        <v>-0.5041508886617859</v>
+        <v>-1.359791178196278</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>1.004939730996509</v>
       </c>
       <c r="E49">
-        <v>-16.34487237866265</v>
+        <v>-18.48530996007613</v>
       </c>
       <c r="F49">
-        <v>-1.989999584503802</v>
+        <v>-2.277938436982105</v>
       </c>
       <c r="G49">
-        <v>-0.519594583602486</v>
+        <v>-1.640684346112359</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.9907605338532336</v>
       </c>
       <c r="E50">
-        <v>-16.03180538509037</v>
+        <v>-18.35515256014767</v>
       </c>
       <c r="F50">
-        <v>-2.127572357658535</v>
+        <v>-2.213597484071861</v>
       </c>
       <c r="G50">
-        <v>-0.4134584936134517</v>
+        <v>-1.993413041685086</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.025463720638223</v>
       </c>
       <c r="E51">
-        <v>-15.58426535586032</v>
+        <v>-17.58960044372897</v>
       </c>
       <c r="F51">
-        <v>-2.11479976067477</v>
+        <v>-2.362678765553688</v>
       </c>
       <c r="G51">
-        <v>-1.132485810924379</v>
+        <v>-1.769553952319569</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.106525917253028</v>
       </c>
       <c r="E52">
-        <v>-15.8278429157849</v>
+        <v>-17.0903271274353</v>
       </c>
       <c r="F52">
-        <v>-2.180492609186382</v>
+        <v>-2.726805881537073</v>
       </c>
       <c r="G52">
-        <v>-0.8290047907938497</v>
+        <v>-1.60211649057985</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.222753047711579</v>
       </c>
       <c r="E53">
-        <v>-14.85599163747277</v>
+        <v>-16.67037003338598</v>
       </c>
       <c r="F53">
-        <v>-2.446270976904992</v>
+        <v>-2.660287979092272</v>
       </c>
       <c r="G53">
-        <v>-0.9563383038708373</v>
+        <v>-2.246534043072222</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.355438438239872</v>
       </c>
       <c r="E54">
-        <v>-14.79180504688805</v>
+        <v>-16.10679691465739</v>
       </c>
       <c r="F54">
-        <v>-2.159976433721247</v>
+        <v>-2.171789781252571</v>
       </c>
       <c r="G54">
-        <v>-0.7652536153441044</v>
+        <v>-2.452655229438325</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>1.482114074424588</v>
       </c>
       <c r="E55">
-        <v>-14.10397965833701</v>
+        <v>-16.96037803731119</v>
       </c>
       <c r="F55">
-        <v>-2.223725932305891</v>
+        <v>-2.777372741273566</v>
       </c>
       <c r="G55">
-        <v>-1.328129120658688</v>
+        <v>-2.375930026020176</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>1.578883111123928</v>
       </c>
       <c r="E56">
-        <v>-13.61486370924254</v>
+        <v>-15.82776140325276</v>
       </c>
       <c r="F56">
-        <v>-2.426831679063496</v>
+        <v>-2.735237833330169</v>
       </c>
       <c r="G56">
-        <v>-1.246173255288491</v>
+        <v>-2.466731669071306</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.622983633317597</v>
       </c>
       <c r="E57">
-        <v>-13.44462025739818</v>
+        <v>-15.06671058999769</v>
       </c>
       <c r="F57">
-        <v>-2.670902678991745</v>
+        <v>-2.683913017420114</v>
       </c>
       <c r="G57">
-        <v>-0.726477195442621</v>
+        <v>-2.262749095123572</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.597741584545846</v>
       </c>
       <c r="E58">
-        <v>-13.75316330543679</v>
+        <v>-14.96273229830757</v>
       </c>
       <c r="F58">
-        <v>-2.132269200832409</v>
+        <v>-2.725857400860867</v>
       </c>
       <c r="G58">
-        <v>-1.161598748396729</v>
+        <v>-1.981091191187919</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.49477226697868</v>
       </c>
       <c r="E59">
-        <v>-12.37324670581948</v>
+        <v>-15.15221723621052</v>
       </c>
       <c r="F59">
-        <v>-2.377892561273504</v>
+        <v>-2.682889155310254</v>
       </c>
       <c r="G59">
-        <v>-1.489028254958346</v>
+        <v>-2.84000892080629</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.313796177096089</v>
       </c>
       <c r="E60">
-        <v>-12.38865710286758</v>
+        <v>-15.30265314274533</v>
       </c>
       <c r="F60">
-        <v>-2.446702556321851</v>
+        <v>-2.869796177506115</v>
       </c>
       <c r="G60">
-        <v>-1.398378897002023</v>
+        <v>-3.241399325260764</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.063028713548896</v>
       </c>
       <c r="E61">
-        <v>-11.65481336145059</v>
+        <v>-14.32587035623885</v>
       </c>
       <c r="F61">
-        <v>-2.347314206966563</v>
+        <v>-2.664153969761138</v>
       </c>
       <c r="G61">
-        <v>-1.300287432673417</v>
+        <v>-2.84972537196405</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.7579737365402381</v>
       </c>
       <c r="E62">
-        <v>-12.82853495407665</v>
+        <v>-14.35615226192814</v>
       </c>
       <c r="F62">
-        <v>-2.514539219671908</v>
+        <v>-2.507333251634955</v>
       </c>
       <c r="G62">
-        <v>-1.993631537690678</v>
+        <v>-3.399057435477475</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>0.4179697925463137</v>
       </c>
       <c r="E63">
-        <v>-12.20954689891621</v>
+        <v>-14.46426052191325</v>
       </c>
       <c r="F63">
-        <v>-2.396299713331112</v>
+        <v>-2.723039294956543</v>
       </c>
       <c r="G63">
-        <v>-1.737663467139769</v>
+        <v>-3.221867106579064</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.06433358148441717</v>
       </c>
       <c r="E64">
-        <v>-11.38466271604901</v>
+        <v>-14.38424691467173</v>
       </c>
       <c r="F64">
-        <v>-2.602615383774565</v>
+        <v>-2.700766980597473</v>
       </c>
       <c r="G64">
-        <v>-1.770811959624492</v>
+        <v>-3.304405627964173</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.2811573713381534</v>
       </c>
       <c r="E65">
-        <v>-11.60727796979208</v>
+        <v>-13.2087139324426</v>
       </c>
       <c r="F65">
-        <v>-2.639345194414696</v>
+        <v>-2.884830217499523</v>
       </c>
       <c r="G65">
-        <v>-1.579545191093099</v>
+        <v>-3.47280645845582</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.5996276828034927</v>
       </c>
       <c r="E66">
-        <v>-11.0611847607331</v>
+        <v>-13.55146507313516</v>
       </c>
       <c r="F66">
-        <v>-2.852286975713142</v>
+        <v>-2.709363777503726</v>
       </c>
       <c r="G66">
-        <v>-1.795200748612303</v>
+        <v>-3.343109215863792</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-0.8759516388561387</v>
       </c>
       <c r="E67">
-        <v>-11.00414410213249</v>
+        <v>-13.06502545217922</v>
       </c>
       <c r="F67">
-        <v>-2.672375516233923</v>
+        <v>-2.881834840971</v>
       </c>
       <c r="G67">
-        <v>-2.204658952545981</v>
+        <v>-3.817460733458264</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.098529945293507</v>
       </c>
       <c r="E68">
-        <v>-10.73360853644025</v>
+        <v>-13.05190193450499</v>
       </c>
       <c r="F68">
-        <v>-2.938264056817105</v>
+        <v>-2.968235217817794</v>
       </c>
       <c r="G68">
-        <v>-1.981173954826401</v>
+        <v>-3.792254239722253</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.262723829169986</v>
       </c>
       <c r="E69">
-        <v>-11.44614580765115</v>
+        <v>-13.02123963699906</v>
       </c>
       <c r="F69">
-        <v>-2.950138703536236</v>
+        <v>-2.798259196967753</v>
       </c>
       <c r="G69">
-        <v>-2.255892955311742</v>
+        <v>-3.571460715526101</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-1.371734284450487</v>
       </c>
       <c r="E70">
-        <v>-10.94236665971985</v>
+        <v>-13.31817620615601</v>
       </c>
       <c r="F70">
-        <v>-2.858397013676191</v>
+        <v>-2.85732841972658</v>
       </c>
       <c r="G70">
-        <v>-2.140593275270005</v>
+        <v>-3.485866560608244</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-1.433376350286335</v>
       </c>
       <c r="E71">
-        <v>-11.61554243485608</v>
+        <v>-13.04663079076006</v>
       </c>
       <c r="F71">
-        <v>-2.948283988921368</v>
+        <v>-3.24323828493398</v>
       </c>
       <c r="G71">
-        <v>-2.156758669138266</v>
+        <v>-3.90792139031885</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-1.460635218277914</v>
       </c>
       <c r="E72">
-        <v>-11.04219686921894</v>
+        <v>-13.77072019916453</v>
       </c>
       <c r="F72">
-        <v>-3.104162853310568</v>
+        <v>-3.220681012188346</v>
       </c>
       <c r="G72">
-        <v>-2.13475678348427</v>
+        <v>-3.176419937415949</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-1.470579646697598</v>
       </c>
       <c r="E73">
-        <v>-10.41940942436606</v>
+        <v>-12.43362032128974</v>
       </c>
       <c r="F73">
-        <v>-2.825907615770991</v>
+        <v>-2.998011712478825</v>
       </c>
       <c r="G73">
-        <v>-1.902181027713851</v>
+        <v>-3.555305253294458</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.478084710139488</v>
       </c>
       <c r="E74">
-        <v>-11.72156306832365</v>
+        <v>-13.74001261691852</v>
       </c>
       <c r="F74">
-        <v>-3.284564706292244</v>
+        <v>-3.450919104857247</v>
       </c>
       <c r="G74">
-        <v>-1.653568989351203</v>
+        <v>-3.149856120008837</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.495310375852443</v>
       </c>
       <c r="E75">
-        <v>-10.98174626969055</v>
+        <v>-13.95200407063959</v>
       </c>
       <c r="F75">
-        <v>-2.925824463529265</v>
+        <v>-3.188102150603644</v>
       </c>
       <c r="G75">
-        <v>-1.00352350944207</v>
+        <v>-2.803079785315719</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.532944698443101</v>
       </c>
       <c r="E76">
-        <v>-11.69653872095727</v>
+        <v>-14.07463061829329</v>
       </c>
       <c r="F76">
-        <v>-3.435146161140541</v>
+        <v>-3.004544217817302</v>
       </c>
       <c r="G76">
-        <v>-1.880976983534819</v>
+        <v>-3.020281367601763</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.596738700500992</v>
       </c>
       <c r="E77">
-        <v>-11.44261359792517</v>
+        <v>-14.36945239008867</v>
       </c>
       <c r="F77">
-        <v>-3.004504456181968</v>
+        <v>-3.301323407218281</v>
       </c>
       <c r="G77">
-        <v>-0.8999034340628814</v>
+        <v>-3.695050001598173</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.688238572839585</v>
       </c>
       <c r="E78">
-        <v>-12.6855121594924</v>
+        <v>-14.318285162276</v>
       </c>
       <c r="F78">
-        <v>-3.159958368093531</v>
+        <v>-3.475043648728977</v>
       </c>
       <c r="G78">
-        <v>-0.5726427653237675</v>
+        <v>-2.724106721476405</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.808056485183497</v>
       </c>
       <c r="E79">
-        <v>-13.29881697977322</v>
+        <v>-15.5433958779411</v>
       </c>
       <c r="F79">
-        <v>-3.416667769486293</v>
+        <v>-3.407612057038889</v>
       </c>
       <c r="G79">
-        <v>-0.7920657236666617</v>
+        <v>-2.592684684658417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.953974425797943</v>
       </c>
       <c r="E80">
-        <v>-13.3469229591567</v>
+        <v>-15.56303586971237</v>
       </c>
       <c r="F80">
-        <v>-3.526085991354677</v>
+        <v>-3.795065999085107</v>
       </c>
       <c r="G80">
-        <v>-0.1041509133338055</v>
+        <v>-2.871551798704465</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.120184515035855</v>
       </c>
       <c r="E81">
-        <v>-14.7773682717516</v>
+        <v>-16.24202620547444</v>
       </c>
       <c r="F81">
-        <v>-3.676406510471092</v>
+        <v>-3.665128288281976</v>
       </c>
       <c r="G81">
-        <v>-0.7529648703023297</v>
+        <v>-2.551488255967727</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.299571251946186</v>
       </c>
       <c r="E82">
-        <v>-15.01356441904367</v>
+        <v>-17.7737553677249</v>
       </c>
       <c r="F82">
-        <v>-3.693693709800114</v>
+        <v>-3.836819029655813</v>
       </c>
       <c r="G82">
-        <v>-0.5843620965327875</v>
+        <v>-2.998726405595568</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.483587196985696</v>
       </c>
       <c r="E83">
-        <v>-15.59246189381421</v>
+        <v>-17.93048585313037</v>
       </c>
       <c r="F83">
-        <v>-3.878236571428386</v>
+        <v>-3.949212747235053</v>
       </c>
       <c r="G83">
-        <v>-0.07324366017916965</v>
+        <v>-2.017325112115242</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.662608795317364</v>
       </c>
       <c r="E84">
-        <v>-17.02171168927108</v>
+        <v>-18.61972865404581</v>
       </c>
       <c r="F84">
-        <v>-3.560242892841711</v>
+        <v>-4.065157675870094</v>
       </c>
       <c r="G84">
-        <v>-0.05763112741596674</v>
+        <v>-2.098344093097826</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.827712122039387</v>
       </c>
       <c r="E85">
-        <v>-17.43649726600365</v>
+        <v>-18.96191373548741</v>
       </c>
       <c r="F85">
-        <v>-3.644781928134415</v>
+        <v>-4.119322963604348</v>
       </c>
       <c r="G85">
-        <v>-0.02044376937333349</v>
+        <v>-2.286465843366911</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.971696757042485</v>
       </c>
       <c r="E86">
-        <v>-18.49994598806892</v>
+        <v>-20.99769828258363</v>
       </c>
       <c r="F86">
-        <v>-4.020157445080414</v>
+        <v>-3.966026948777077</v>
       </c>
       <c r="G86">
-        <v>0.01470760316264797</v>
+        <v>-2.450073003917693</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.089301678779036</v>
       </c>
       <c r="E87">
-        <v>-20.06926601305705</v>
+        <v>-21.70870945805395</v>
       </c>
       <c r="F87">
-        <v>-4.038475133458519</v>
+        <v>-4.144785320831599</v>
       </c>
       <c r="G87">
-        <v>0.1395085489020932</v>
+        <v>-2.497940181870015</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.178592492464295</v>
       </c>
       <c r="E88">
-        <v>-22.51307965366639</v>
+        <v>-23.22072617294901</v>
       </c>
       <c r="F88">
-        <v>-4.139329693116761</v>
+        <v>-4.293286745131467</v>
       </c>
       <c r="G88">
-        <v>0.3570842228340741</v>
+        <v>-1.792817155824027</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.242785344588603</v>
       </c>
       <c r="E89">
-        <v>-22.8847315154759</v>
+        <v>-25.51175815748757</v>
       </c>
       <c r="F89">
-        <v>-4.066675244952022</v>
+        <v>-4.634152476076838</v>
       </c>
       <c r="G89">
-        <v>-0.2958281895120679</v>
+        <v>-2.174019853580026</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.288634228508672</v>
       </c>
       <c r="E90">
-        <v>-25.3107482532351</v>
+        <v>-26.69994822456814</v>
       </c>
       <c r="F90">
-        <v>-4.408170535123522</v>
+        <v>-4.381703368236675</v>
       </c>
       <c r="G90">
-        <v>-0.1980181215543007</v>
+        <v>-2.350905612288825</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.325118396633993</v>
       </c>
       <c r="E91">
-        <v>-26.98108494791233</v>
+        <v>-29.21387169976424</v>
       </c>
       <c r="F91">
-        <v>-4.300995532181918</v>
+        <v>-4.523933222929947</v>
       </c>
       <c r="G91">
-        <v>0.1815690299785336</v>
+        <v>-1.982690184683387</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.364486441081869</v>
       </c>
       <c r="E92">
-        <v>-28.8877808149459</v>
+        <v>-30.55168707653224</v>
       </c>
       <c r="F92">
-        <v>-4.36375264661801</v>
+        <v>-4.295440500378746</v>
       </c>
       <c r="G92">
-        <v>-0.8289981697027712</v>
+        <v>-2.143791262260941</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.418627087086495</v>
       </c>
       <c r="E93">
-        <v>-31.20450056829297</v>
+        <v>-32.7192117252226</v>
       </c>
       <c r="F93">
-        <v>-4.284863905379801</v>
+        <v>-4.244566316335813</v>
       </c>
       <c r="G93">
-        <v>-0.5113314619364651</v>
+        <v>-2.406830658083733</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.495649564769266</v>
       </c>
       <c r="E94">
-        <v>-32.82084879585076</v>
+        <v>-34.57392750335913</v>
       </c>
       <c r="F94">
-        <v>-4.202916003323055</v>
+        <v>-4.750341773095705</v>
       </c>
       <c r="G94">
-        <v>-0.6180204130305577</v>
+        <v>-2.708917938542229</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.603005716890384</v>
       </c>
       <c r="E95">
-        <v>-35.63960876311019</v>
+        <v>-36.71198990015559</v>
       </c>
       <c r="F95">
-        <v>-4.308704319232371</v>
+        <v>-4.710387128156476</v>
       </c>
       <c r="G95">
-        <v>-1.022254576103266</v>
+        <v>-2.68761126745148</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.742489816168248</v>
       </c>
       <c r="E96">
-        <v>-37.84959011985947</v>
+        <v>-38.50436896933954</v>
       </c>
       <c r="F96">
-        <v>-4.317373184102668</v>
+        <v>-4.647793202098738</v>
       </c>
       <c r="G96">
-        <v>-1.203288448372771</v>
+        <v>-3.268717947050829</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.909584039369912</v>
       </c>
       <c r="E97">
-        <v>-40.53536918364666</v>
+        <v>-41.07794376840167</v>
       </c>
       <c r="F97">
-        <v>-4.210431780768655</v>
+        <v>-4.903188812790659</v>
       </c>
       <c r="G97">
-        <v>-1.488306556030785</v>
+        <v>-3.768782471848821</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.094914837032677</v>
       </c>
       <c r="E98">
-        <v>-42.08323556302344</v>
+        <v>-43.79049517052221</v>
       </c>
       <c r="F98">
-        <v>-4.322940641416883</v>
+        <v>-4.786418830222429</v>
       </c>
       <c r="G98">
-        <v>-2.209922719953422</v>
+        <v>-3.862507326611127</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.284755596947387</v>
       </c>
       <c r="E99">
-        <v>-44.94673685347866</v>
+        <v>-45.54813857983032</v>
       </c>
       <c r="F99">
-        <v>-4.247113546099422</v>
+        <v>-4.618974300155343</v>
       </c>
       <c r="G99">
-        <v>-2.496049860367092</v>
+        <v>-4.062225917904279</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.456624463512699</v>
       </c>
       <c r="E100">
-        <v>-47.66179476596244</v>
+        <v>-47.65853426467692</v>
       </c>
       <c r="F100">
-        <v>-4.404786654283086</v>
+        <v>-4.874028623477311</v>
       </c>
       <c r="G100">
-        <v>-3.07043944306726</v>
+        <v>-5.099413214266864</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.591135516199616</v>
       </c>
       <c r="E101">
-        <v>-49.0672983758416</v>
+        <v>-50.53827466292364</v>
       </c>
       <c r="F101">
-        <v>-4.397465543177144</v>
+        <v>-4.657687222357775</v>
       </c>
       <c r="G101">
-        <v>-3.673915478875466</v>
+        <v>-5.969050490341394</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.659518621783683</v>
       </c>
       <c r="E102">
-        <v>-52.29878459627861</v>
+        <v>-53.18072528740544</v>
       </c>
       <c r="F102">
-        <v>-4.370180777663734</v>
+        <v>-4.944507778842298</v>
       </c>
       <c r="G102">
-        <v>-4.277742432510834</v>
+        <v>-5.852562324451059</v>
       </c>
     </row>
   </sheetData>
